--- a/data/trans_camb/DC-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/DC-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -6,24</t>
+          <t>-13,63; -6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -8,17</t>
+          <t>-15,79; -8,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 11,08</t>
+          <t>1,86; 11,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,2</t>
+          <t>-6,9; 0,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -4,44</t>
+          <t>-12,05; -4,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 24,28</t>
+          <t>16,69; 24,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -3,6</t>
+          <t>-8,63; -3,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -7,05</t>
+          <t>-12,88; -7,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,96</t>
+          <t>11,91; 17,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -23,57</t>
+          <t>-46,54; -23,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; -31,08</t>
+          <t>-53,85; -32,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 42,69</t>
+          <t>6,34; 45,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 0,53</t>
+          <t>-18,98; 1,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -13,48</t>
+          <t>-33,53; -13,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,47; 74,2</t>
+          <t>45,53; 73,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -11,71</t>
+          <t>-26,55; -11,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,58; -22,81</t>
+          <t>-39,25; -23,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,01; 59,93</t>
+          <t>36,56; 59,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -2,79</t>
+          <t>-6,77; -2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -3,18</t>
+          <t>-7,47; -3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,31</t>
+          <t>-1,03; 8,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -1,63</t>
+          <t>-7,5; -1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; -5,36</t>
+          <t>-10,75; -5,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 32,87</t>
+          <t>10,39; 34,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -2,94</t>
+          <t>-6,66; -3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -4,87</t>
+          <t>-8,31; -4,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 22,54</t>
+          <t>5,93; 21,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,1; -23,45</t>
+          <t>-47,95; -24,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,23; -26,76</t>
+          <t>-51,99; -28,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 67,63</t>
+          <t>-6,04; 66,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -7,25</t>
+          <t>-29,08; -6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; -24,12</t>
+          <t>-42,49; -22,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,74; 139,54</t>
+          <t>42,11; 155,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,69; -16,95</t>
+          <t>-34,07; -17,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,68; -28,42</t>
+          <t>-42,96; -28,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 122,68</t>
+          <t>30,54; 118,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -3,72</t>
+          <t>-10,9; -3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -0,49</t>
+          <t>-7,89; -0,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,06</t>
+          <t>-0,14; 8,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 1,81</t>
+          <t>-8,54; 1,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -4,47</t>
+          <t>-13,77; -3,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 15,98</t>
+          <t>5,56; 15,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -1,85</t>
+          <t>-8,49; -1,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -2,9</t>
+          <t>-9,47; -3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,21</t>
+          <t>4,63; 11,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,3; -35,2</t>
+          <t>-75,16; -31,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -3,1</t>
+          <t>-55,29; -3,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 75,65</t>
+          <t>-1,68; 74,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 10,15</t>
+          <t>-33,5; 10,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,65; -22,53</t>
+          <t>-54,72; -17,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,91; 83,98</t>
+          <t>21,29; 82,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,42; -11,2</t>
+          <t>-45,99; -10,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -19,44</t>
+          <t>-50,11; -22,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,3; 74,91</t>
+          <t>23,83; 72,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -5,42</t>
+          <t>-8,8; -5,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -6,3</t>
+          <t>-9,68; -6,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,96</t>
+          <t>-2,03; 4,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -2,04</t>
+          <t>-6,21; -1,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -7,4</t>
+          <t>-11,5; -7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,55; 25,19</t>
+          <t>10,63; 25,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -4,06</t>
+          <t>-6,94; -4,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -7,34</t>
+          <t>-9,93; -7,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 15,82</t>
+          <t>5,53; 15,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -32,41</t>
+          <t>-48,12; -33,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,03; -37,7</t>
+          <t>-52,17; -37,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 29,4</t>
+          <t>-10,73; 28,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,75; -7,45</t>
+          <t>-21,41; -7,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,68; -27,15</t>
+          <t>-39,74; -27,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,22; 91,39</t>
+          <t>37,94; 92,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -18,38</t>
+          <t>-29,34; -18,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,66; -33,2</t>
+          <t>-42,3; -33,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,8; 69,03</t>
+          <t>23,96; 69,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DC-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/DC-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,41</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,09</t>
+          <t>14,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -6,1</t>
+          <t>-13,95; -6,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -8,03</t>
+          <t>-15,83; -8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 11,81</t>
+          <t>0,83; 9,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,21</t>
+          <t>-7,09; 0,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -4,42</t>
+          <t>-11,93; -3,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 24,1</t>
+          <t>16,63; 24,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -3,43</t>
+          <t>-8,91; -3,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -7,12</t>
+          <t>-12,85; -7,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 17,94</t>
+          <t>11,31; 17,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -23,85</t>
+          <t>-47,64; -25,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,85; -32,0</t>
+          <t>-53,36; -31,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 45,95</t>
+          <t>2,88; 37,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 1,01</t>
+          <t>-19,85; 1,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,53; -13,45</t>
+          <t>-33,34; -11,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,53; 73,89</t>
+          <t>45,11; 75,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,55; -11,67</t>
+          <t>-27,13; -11,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,25; -23,32</t>
+          <t>-39,17; -23,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,56; 59,91</t>
+          <t>34,52; 57,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>8,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -2,93</t>
+          <t>-6,87; -2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -3,35</t>
+          <t>-7,18; -3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 8,08</t>
+          <t>4,5; 9,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -1,55</t>
+          <t>-7,27; -1,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -5,21</t>
+          <t>-10,61; -5,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 34,9</t>
+          <t>7,56; 13,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -3,07</t>
+          <t>-6,56; -3,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -4,96</t>
+          <t>-8,25; -4,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 21,34</t>
+          <t>6,94; 10,87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -24,57</t>
+          <t>-48,84; -22,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,99; -28,47</t>
+          <t>-51,16; -27,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 66,1</t>
+          <t>32,2; 80,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,08; -6,93</t>
+          <t>-28,82; -6,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,49; -22,83</t>
+          <t>-41,72; -25,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,11; 155,82</t>
+          <t>28,97; 58,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,07; -17,41</t>
+          <t>-34,07; -18,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,96; -28,36</t>
+          <t>-42,79; -28,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,54; 118,55</t>
+          <t>35,56; 62,16</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,99</t>
+          <t>11,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>8,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -3,36</t>
+          <t>-11,26; -3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,42</t>
+          <t>-8,06; -0,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,26</t>
+          <t>-0,71; 7,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 1,62</t>
+          <t>-8,91; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -3,66</t>
+          <t>-13,74; -4,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 15,97</t>
+          <t>6,43; 16,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -1,58</t>
+          <t>-8,51; -2,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; -3,5</t>
+          <t>-9,19; -3,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,3</t>
+          <t>4,71; 11,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,16; -31,31</t>
+          <t>-75,24; -36,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -3,75</t>
+          <t>-56,08; -4,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 74,61</t>
+          <t>-5,38; 72,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 10,94</t>
+          <t>-35,35; 11,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -17,97</t>
+          <t>-55,64; -22,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,29; 82,64</t>
+          <t>26,49; 84,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,99; -10,74</t>
+          <t>-45,64; -12,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,11; -22,19</t>
+          <t>-49,18; -20,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,83; 72,87</t>
+          <t>24,13; 73,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -5,52</t>
+          <t>-8,9; -5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -6,32</t>
+          <t>-9,75; -6,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,81</t>
+          <t>2,04; 5,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -1,9</t>
+          <t>-6,12; -1,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -7,43</t>
+          <t>-11,55; -7,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,63; 25,0</t>
+          <t>8,69; 13,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -4,18</t>
+          <t>-6,87; -4,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -7,34</t>
+          <t>-10,06; -7,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 15,53</t>
+          <t>6,13; 9,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,12; -33,1</t>
+          <t>-48,35; -32,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,17; -37,99</t>
+          <t>-51,98; -38,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 28,89</t>
+          <t>11,16; 34,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -7,1</t>
+          <t>-21,1; -7,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -27,5</t>
+          <t>-39,72; -27,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,94; 92,71</t>
+          <t>29,51; 48,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,34; -18,82</t>
+          <t>-29,24; -19,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,3; -33,31</t>
+          <t>-42,8; -33,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,96; 69,6</t>
+          <t>26,08; 41,46</t>
         </is>
       </c>
     </row>
